--- a/AZN.xlsx
+++ b/AZN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B22DCB2-2D89-4937-8BF1-35CD236AED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4BB35BF-460C-4335-A97F-21F70075C06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="2620" windowWidth="26100" windowHeight="18090" tabRatio="524" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14410" yWindow="4280" windowWidth="19050" windowHeight="16100" tabRatio="524" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="32" r:id="rId1"/>
@@ -8402,7 +8402,7 @@
         <v>957</v>
       </c>
       <c r="K1" s="24">
-        <v>15294</v>
+        <v>12630</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -8431,7 +8431,7 @@
         <v>179</v>
       </c>
       <c r="K2" s="26">
-        <v>202</v>
+        <v>168.34</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -8460,10 +8460,10 @@
         <v>180</v>
       </c>
       <c r="K3" s="24">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L3" s="132" t="s">
-        <v>611</v>
+        <v>958</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="K4" s="24">
         <f>K2*K3</f>
-        <v>315524</v>
+        <v>262778.74</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="132" t="s">
-        <v>611</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -8552,10 +8552,10 @@
         <v>875</v>
       </c>
       <c r="K6" s="24">
-        <v>23374</v>
+        <v>25944</v>
       </c>
       <c r="L6" s="132" t="s">
-        <v>611</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="K7" s="24">
         <f>K4-K5+K6</f>
-        <v>338898</v>
+        <v>288722.74</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="EP107" s="34">
         <f>NPV($EP$106,DP100:GU100)+Main!K5-Main!K6+DO100</f>
-        <v>73317.337645462452</v>
+        <v>70747.337645462452</v>
       </c>
     </row>
     <row r="108" spans="1:200">
@@ -42458,7 +42458,7 @@
       </c>
       <c r="EP108" s="50">
         <f>EP107/Main!K3</f>
-        <v>46.938116290308869</v>
+        <v>45.321805025920852</v>
       </c>
     </row>
     <row r="109" spans="1:200">
@@ -43542,7 +43542,7 @@
         <v>0.12562189054726369</v>
       </c>
       <c r="CW113" s="112">
-        <f t="shared" ref="CW113:DF114" si="236">+CW3/CS3-1</f>
+        <f t="shared" ref="CW113:CX114" si="236">+CW3/CS3-1</f>
         <v>0.11350059737156504</v>
       </c>
       <c r="CX113" s="112">
@@ -53826,15 +53826,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100764A4B226BE2F34C80DFAA3D37A3CB30" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="70544b0716d1f2dd0e24adda29a3d132">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b05d82d297216baf5b26c55225140df">
     <xsd:element name="properties">
@@ -53948,6 +53939,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553A2183-5DA3-4AC7-A24E-386811F0FD0B}">
   <ds:schemaRefs>
@@ -53958,14 +53958,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DA31EBE-4993-4E59-ACFD-7F137917727B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8771156D-B6D2-4C3E-9AA3-02F85B74489D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -53979,4 +53971,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DA31EBE-4993-4E59-ACFD-7F137917727B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>